--- a/output/laminas_comunales/comunal_s_fonasa_a_2023_la_araucania.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2023_la_araucania.xlsx
@@ -375,481 +375,481 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Temuco</t>
+          <t>Nueva Imperial</t>
         </is>
       </c>
       <c r="C2">
-        <v>251037</v>
+        <v>95.3397013318983</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Padre Las Casas</t>
+          <t>Carahue</t>
         </is>
       </c>
       <c r="C3">
-        <v>77174</v>
+        <v>95.19029233314947</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Villarrica</t>
+          <t>Ercilla</t>
         </is>
       </c>
       <c r="C4">
-        <v>67832</v>
+        <v>94.90103270223752</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Angol</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="C5">
-        <v>53021</v>
+        <v>94.73351590478197</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9108</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lautaro</t>
+          <t>Los Sauces</t>
         </is>
       </c>
       <c r="C6">
-        <v>41392</v>
+        <v>94.72140762463343</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nueva Imperial</t>
+          <t>Purén</t>
         </is>
       </c>
       <c r="C7">
-        <v>35433</v>
+        <v>94.63724650099971</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Galvarino</t>
         </is>
       </c>
       <c r="C8">
-        <v>33943</v>
+        <v>94.41270263087962</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pucón</t>
+          <t>Loncoche</t>
         </is>
       </c>
       <c r="C9">
-        <v>33646</v>
+        <v>94.16608462301951</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vilcún</t>
+          <t>Cholchol</t>
         </is>
       </c>
       <c r="C10">
-        <v>31369</v>
+        <v>94.11352978231959</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pitrufquén</t>
+          <t>Cunco</t>
         </is>
       </c>
       <c r="C11">
-        <v>27078</v>
+        <v>93.91568264807701</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Collipulli</t>
+          <t>Lumaco</t>
         </is>
       </c>
       <c r="C12">
-        <v>26224</v>
+        <v>93.81538461538462</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Freire</t>
+          <t>Teodoro Schmidt</t>
         </is>
       </c>
       <c r="C13">
-        <v>25939</v>
+        <v>93.64244468583843</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Carahue</t>
+          <t>Curarrehue</t>
         </is>
       </c>
       <c r="C14">
-        <v>25887</v>
+        <v>93.60215053763442</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Loncoche</t>
+          <t>Toltén</t>
         </is>
       </c>
       <c r="C15">
-        <v>25616</v>
+        <v>93.5932142212597</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cunco</t>
+          <t>Freire</t>
         </is>
       </c>
       <c r="C16">
-        <v>19804</v>
+        <v>93.56153513201558</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Traiguén</t>
+          <t>Perquenco</t>
         </is>
       </c>
       <c r="C17">
-        <v>19289</v>
+        <v>93.36053412462908</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Curacautín</t>
+          <t>Gorbea</t>
         </is>
       </c>
       <c r="C18">
-        <v>18860</v>
+        <v>93.18728466488982</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Teodoro Schmidt</t>
+          <t>Renaico</t>
         </is>
       </c>
       <c r="C19">
-        <v>16379</v>
+        <v>93.11560150375939</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gorbea</t>
+          <t>Padre Las Casas</t>
         </is>
       </c>
       <c r="C20">
-        <v>14335</v>
+        <v>93.08839139245393</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Galvarino</t>
+          <t>Collipulli</t>
         </is>
       </c>
       <c r="C21">
-        <v>14211</v>
+        <v>92.98631302744487</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>9108</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Lautaro</t>
         </is>
       </c>
       <c r="C22">
-        <v>13491</v>
+        <v>92.90716466151912</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cholchol</t>
+          <t>Lonquimay</t>
         </is>
       </c>
       <c r="C23">
-        <v>13446</v>
+        <v>92.26321361674404</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Purén</t>
+          <t>Pitrufquén</t>
         </is>
       </c>
       <c r="C24">
-        <v>13253</v>
+        <v>92.05820357652819</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Renaico</t>
+          <t>Melipeuco</t>
         </is>
       </c>
       <c r="C25">
-        <v>11889</v>
+        <v>91.92139737991266</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9205</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lonquimay</t>
+          <t>Vilcún</t>
         </is>
       </c>
       <c r="C26">
-        <v>11329</v>
+        <v>91.74099961980522</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Toltén</t>
+          <t>Traiguén</t>
         </is>
       </c>
       <c r="C27">
-        <v>10372</v>
+        <v>91.16646185839872</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lumaco</t>
+          <t>Curacautín</t>
         </is>
       </c>
       <c r="C28">
-        <v>9147</v>
+        <v>90.25218930947025</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ercilla</t>
+          <t>Angol</t>
         </is>
       </c>
       <c r="C29">
-        <v>8822</v>
+        <v>89.84782756049617</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Curarrehue</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="C30">
-        <v>8705</v>
+        <v>89.78442005025791</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Perquenco</t>
+          <t>Villarrica</t>
         </is>
       </c>
       <c r="C31">
-        <v>7551</v>
+        <v>89.6016062559442</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Los Sauces</t>
+          <t>Pucón</t>
         </is>
       </c>
       <c r="C32">
-        <v>7429</v>
+        <v>88.25180327868853</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Melipeuco</t>
+          <t>Temuco</t>
         </is>
       </c>
       <c r="C33">
-        <v>7157</v>
+        <v>82.8245269634933</v>
       </c>
     </row>
   </sheetData>
@@ -905,7 +905,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
